--- a/_presentations/budget mobilités et territoires.xlsx
+++ b/_presentations/budget mobilités et territoires.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timbe\github\meaps\_presentations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AA59F5-96E1-4128-BD2B-A459F75B5FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE33E9D-9B73-4CDC-80B7-5DABEC1DA4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="71">
   <si>
     <t xml:space="preserve">Ressources </t>
   </si>
@@ -238,13 +238,16 @@
     <t>Site web&amp;communication</t>
   </si>
   <si>
-    <t>Frais de structure OFCE</t>
-  </si>
-  <si>
     <t>Frais de gestion (Sciences Po 15%)</t>
   </si>
   <si>
     <t>Total Dépenses</t>
+  </si>
+  <si>
+    <t>Frais de structure (OFCE)</t>
+  </si>
+  <si>
+    <t>Total hors frais</t>
   </si>
 </sst>
 </file>
@@ -256,7 +259,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00\ [$€-40C]_-;\-* #,##0.00\ [$€-40C]_-;_-* &quot;-&quot;??\ [$€-40C]_-;_-@"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
-    <numFmt numFmtId="169" formatCode="#,##0\ [$€-1]"/>
+    <numFmt numFmtId="168" formatCode="#,##0\ [$€-1]"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -718,8 +721,8 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -958,7 +961,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -978,7 +981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
@@ -988,7 +991,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
@@ -998,7 +1001,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1016,7 +1019,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="C8" s="3" t="s">
         <v>8</v>
       </c>
@@ -1108,7 +1111,7 @@
       </c>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="C13" s="3" t="s">
         <v>16</v>
       </c>
@@ -1192,7 +1195,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="C18" s="6" t="s">
         <v>20</v>
       </c>
@@ -4216,7 +4219,7 @@
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="14" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>23</v>
       </c>
@@ -4258,7 +4261,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="14" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>29</v>
       </c>
@@ -5284,7 +5287,7 @@
     </row>
     <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="61" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="B7" s="68">
         <f>SUM(B2:B6)</f>
@@ -5309,7 +5312,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="62" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B8" s="67">
         <f>B7*$G$8</f>
@@ -5334,7 +5337,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B9" s="67">
         <f>B7*$G$9</f>
@@ -5361,7 +5364,7 @@
     </row>
     <row r="10" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B10" s="68">
         <f t="shared" ref="B10:E10" si="1">B7+B9</f>
